--- a/tools/importer/reports/import-landing-page.report.xlsx
+++ b/tools/importer/reports/import-landing-page.report.xlsx
@@ -187,7 +187,7 @@
     <t>landing-page</t>
   </si>
   <si>
-    <t>2026-10-24T12:54:33.953Z</t>
+    <t>2026-10-26T13:21:13.131Z</t>
   </si>
   <si>
     <t>Suncorp Australia | Insurance</t>
